--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15314</v>
+        <v>14745</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>170</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2599</v>
+        <v>2504</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2685.9</v>
+        <v>2595.2</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3103</v>
+        <v>2855</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>712</v>
+        <v>663</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>90.7</v>
+        <v>83.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>732.5</v>
+        <v>683.1</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>663.8</v>
+        <v>664.3</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4310</v>
+        <v>3846</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1265</v>
+        <v>1173</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>95.8</v>
+        <v>85.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1283</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2517</v>
+        <v>2271</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>850</v>
+        <v>769</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>92.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>857.9</v>
+        <v>776.6</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2843</v>
+        <v>2701</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>84.7</v>
+        <v>80.5</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>403.5</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="9">
@@ -757,19 +757,19 @@
         <v>18075</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4100</v>
+        <v>4067</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>88.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>104.8</v>
+        <v>105.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4204.8</v>
+        <v>4172.5</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8550</v>
+        <v>8401</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1659</v>
+        <v>1625</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>80.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28.6</v>
+        <v>28.2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1687.6</v>
+        <v>1653.2</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15702</v>
+        <v>14909</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3308</v>
+        <v>3127</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>87.8</v>
+        <v>83.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>61.1</v>
+        <v>56.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3369.1</v>
+        <v>3183.5</v>
       </c>
     </row>
     <row r="12">
@@ -859,19 +859,19 @@
         <v>10670</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1842</v>
+        <v>1794</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>75.7</v>
+        <v>80.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1917.7</v>
+        <v>1874.3</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10755</v>
+        <v>10960</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2528</v>
+        <v>2564</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>117</v>
+        <v>119.2</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2572.9</v>
+        <v>2610.8</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>657</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4360</v>
+        <v>4510</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>102.6</v>
+        <v>106.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>763.8</v>
+        <v>776.4</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7867</v>
+        <v>7506</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1382</v>
+        <v>1295</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>100.9</v>
+        <v>96.2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>100.7</v>
+        <v>93.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1482.7</v>
+        <v>1388.5</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7870</v>
+        <v>7646</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1372</v>
+        <v>1314</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>102.9</v>
+        <v>97.8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1474.9</v>
+        <v>1411.8</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4300</v>
+        <v>4207</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1153</v>
+        <v>1117</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>88.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1207.8</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>1769</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6518</v>
+        <v>6291</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1552</v>
+        <v>1475</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1647.1</v>
+        <v>1570.7</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8440</v>
+        <v>8170</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1817</v>
+        <v>1726</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1844.2</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8862</v>
+        <v>8325</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1496</v>
+        <v>1402</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>96.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1506.8</v>
+        <v>1412.3</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6056</v>
+        <v>5870</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1168</v>
+        <v>1090</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22.7</v>
+        <v>20.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1190.7</v>
+        <v>1110.6</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13930</v>
+        <v>13870</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2145</v>
+        <v>2195</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>90.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>115.5</v>
+        <v>115.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2260.5</v>
+        <v>2310.2</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>94.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>26.5</v>
+        <v>27.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>556.5</v>
+        <v>546.2</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8300</v>
+        <v>8046</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2658</v>
+        <v>2570</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2666.4</v>
+        <v>2578.7</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2093</v>
+        <v>2153</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>525.4</v>
+        <v>535.3</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>36447</v>
+        <v>35295</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1058.5</v>
+        <v>1049.7</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>37505.5</v>
+        <v>36344.7</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>30001</v>
+        <v>28334</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6481</v>
+        <v>6137</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>62957</v>
+        <v>61714</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12802</v>
+        <v>12428</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>87.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>28848</v>
+        <v>28065</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>167</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4809</v>
+        <v>4687</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>91.8</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>56079</v>
+        <v>55367</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12356</v>
+        <v>12043</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>87.90000000000001</v>
+        <v>86.8</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>74.7</v>
+        <v>69</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1100</v>
+        <v>-1350</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>50.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>93.3</v>
+        <v>106.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>666</v>
+        <v>848</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>466</v>
+        <v>648</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>23.2</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>97.8</v>
+        <v>95.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>49.3</v>
+        <v>46.5</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-360</v>
+        <v>-380</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>178</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -1807,25 +1807,25 @@
         <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-150</v>
+        <v>-220</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>107.5</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>880</v>
+        <v>750</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-70</v>
+        <v>-200</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>730</v>
+        <v>650</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>104.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>30</v>
+        <v>-50</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
@@ -2020,7 +2020,7 @@
         <v>6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>1</v>
@@ -2059,25 +2059,25 @@
         <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-80</v>
+        <v>-120</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -2104,10 +2104,10 @@
         <v>325</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>77.40000000000001</v>
@@ -2185,19 +2185,19 @@
         <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>178</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>62.2</v>
+        <v>66.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>2.1</v>
@@ -2227,19 +2227,19 @@
         <v>50</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>116.7</v>
+        <v>110</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.1</v>
@@ -2314,10 +2314,10 @@
         <v>3300</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>88</v>
@@ -2353,25 +2353,25 @@
         <v>652</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>231</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>693</v>
+        <v>716</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>103.4</v>
+        <v>106.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -2437,25 +2437,25 @@
         <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>75.8</v>
+        <v>72.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-400</v>
+        <v>-450</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>71</v>
+        <v>72.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-450</v>
+        <v>-430</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>690</v>
+        <v>635</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>38.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>120.8</v>
+        <v>116.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2300</v>
+        <v>2280</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1400</v>
+        <v>-1420</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>337</v>
+        <v>414</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>87.8</v>
+        <v>112.2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-250</v>
+        <v>250</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>73.5</v>
+        <v>75.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-53</v>
+        <v>-49</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2050</v>
+        <v>2130</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>140.4</v>
+        <v>145.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1520</v>
+        <v>1620</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>156.7</v>
+        <v>167</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-60</v>
+        <v>-55</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>93</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>125</v>
+        <v>133.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>194</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>106.1</v>
+        <v>97</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>76.8</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>178</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>107.9</v>
+        <v>105.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>269</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>83.3</v>
+        <v>76.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-250</v>
+        <v>-350</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>62.6</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="43">
@@ -3238,10 +3238,10 @@
         <v>1030</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>103</v>
@@ -3322,10 +3322,10 @@
         <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>80</v>
@@ -3361,25 +3361,25 @@
         <v>179</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>114.3</v>
+        <v>111.4</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="47">
@@ -3403,19 +3403,19 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>41.6</v>
+        <v>35.3</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-111</v>
+        <v>-123</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>2.6</v>
@@ -3445,25 +3445,25 @@
         <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>51.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>229</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>132.4</v>
+        <v>127.5</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>43.1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1630</v>
+        <v>1670</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>65.2</v>
+        <v>66.8</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-870</v>
+        <v>-830</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1800</v>
+        <v>1860</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>166</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3742,10 +3742,10 @@
         <v>1700</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I55" s="4" t="n">
         <v>109.7</v>
@@ -3823,25 +3823,25 @@
         <v>163</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>73.8</v>
+        <v>61.5</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-170</v>
+        <v>-250</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="59">
@@ -3952,10 +3952,10 @@
         <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>71.40000000000001</v>
@@ -3991,25 +3991,25 @@
         <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>107.1</v>
+        <v>103.6</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
@@ -4075,25 +4075,25 @@
         <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>75.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-170</v>
+        <v>-160</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1550</v>
+        <v>1615</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>93</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>140.9</v>
+        <v>146.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>450</v>
+        <v>515</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>949</v>
+        <v>990</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>118.6</v>
+        <v>123.8</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4204,10 +4204,10 @@
         <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>78.7</v>
@@ -4243,25 +4243,25 @@
         <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>335</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>159.8</v>
+        <v>164.9</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>580</v>
+        <v>630</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>550</v>
+        <v>695</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>154.9</v>
+        <v>195.8</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.08.pdf</t>
+          <t>Revenue Meeting_2026.09.15.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T08:20:23.504634Z</t>
+          <t>2026-09-16T08:50:02.774805Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.08</t>
+          <t>2026.09.15</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>14745</v>
+        <v>13923</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2504</v>
+        <v>2346</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>86.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>91.2</v>
+        <v>79.3</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2595.2</v>
+        <v>2425.3</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2855</v>
+        <v>2730</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>663</v>
+        <v>625</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>83.5</v>
+        <v>79.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20.1</v>
+        <v>18.7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>683.1</v>
+        <v>643.7</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1916</v>
+        <v>1774</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>653</v>
+        <v>604</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.7</v>
+        <v>80.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>664.3</v>
+        <v>614.3</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>85.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1189</v>
+        <v>1182.5</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2271</v>
+        <v>2286</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>83.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>776.6</v>
+        <v>783.2</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2701</v>
+        <v>2703</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>376.5</v>
+        <v>376.3</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>18075</v>
+        <v>17719</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>225</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4067</v>
+        <v>3993</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>88.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>105.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4172.5</v>
+        <v>4098.5</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8401</v>
+        <v>8065</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1625</v>
+        <v>1564</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1653.2</v>
+        <v>1589.5</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14909</v>
+        <v>14363</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3127</v>
+        <v>3024</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>83.3</v>
+        <v>80.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>56.5</v>
+        <v>51.9</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3183.5</v>
+        <v>3075.9</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10670</v>
+        <v>10790</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>83.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1874.3</v>
+        <v>1883.4</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10960</v>
+        <v>10965</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2564</v>
+        <v>2572</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>119.2</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2610.8</v>
+        <v>2619.5</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>657</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4510</v>
+        <v>4575</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>106.1</v>
+        <v>107.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>776.4</v>
+        <v>785.2</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7506</v>
+        <v>7431</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>172</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1295</v>
+        <v>1281</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>93.5</v>
+        <v>95.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1388.5</v>
+        <v>1376.7</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7646</v>
+        <v>7570</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>172</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1411.8</v>
+        <v>1400.3</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4207</v>
+        <v>4071</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>266</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>54</v>
+        <v>50.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1171</v>
+        <v>1133.9</v>
       </c>
     </row>
     <row r="18">
@@ -1066,16 +1066,16 @@
         <v>234</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>95.7</v>
+        <v>92.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1570.7</v>
+        <v>1563.2</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8170</v>
+        <v>8100</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1726</v>
+        <v>1719</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1754</v>
+        <v>1746.8</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8325</v>
+        <v>8150</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>168</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1402</v>
+        <v>1366</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1412.3</v>
+        <v>1376.1</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5870</v>
+        <v>5725</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1090</v>
+        <v>1046</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>84.8</v>
+        <v>82.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1110.6</v>
+        <v>1065.1</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13870</v>
+        <v>13210</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2195</v>
+        <v>2042</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>115.2</v>
+        <v>105.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2310.2</v>
+        <v>2147.4</v>
       </c>
     </row>
     <row r="23">
@@ -1230,7 +1230,7 @@
         <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94</v>
@@ -1242,10 +1242,10 @@
         <v>94.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>546.2</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8046</v>
+        <v>7980</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2570</v>
+        <v>2554</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2578.7</v>
+        <v>2562.5</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2153</v>
+        <v>2100</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>100.1</v>
+        <v>97.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>535.3</v>
+        <v>520.6</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>35295</v>
+        <v>34505</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1049.7</v>
+        <v>1012.9</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>36344.7</v>
+        <v>35517.9</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>28334</v>
+        <v>27263</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6137</v>
+        <v>5894</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>85</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>61714</v>
+        <v>60468</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>201</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12428</v>
+        <v>12170</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>86.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>28065</v>
+        <v>27085</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4687</v>
+        <v>4454</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>55367</v>
+        <v>55090</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>218</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12043</v>
+        <v>11988</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>609</v>
+        <v>494</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>69</v>
+        <v>55.2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1350</v>
+        <v>-1950</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>204</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>326</v>
+        <v>265</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>106.7</v>
+        <v>86.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>104</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>424</v>
+        <v>427.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>880</v>
+        <v>810</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>95.7</v>
+        <v>88</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-40</v>
+        <v>-110</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>298</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>46.5</v>
+        <v>40.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-380</v>
+        <v>-420</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>358</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>66.2</v>
+        <v>61.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-220</v>
+        <v>-250</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-200</v>
+        <v>-270</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-50</v>
+        <v>-140</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>80</v>
+        <v>76.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>354</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-95</v>
+        <v>-110</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2185,25 +2185,25 @@
         <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>66.7</v>
+        <v>72</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-150</v>
+        <v>-126</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2230,10 +2230,10 @@
         <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>110</v>
@@ -2269,25 +2269,25 @@
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -2314,10 +2314,10 @@
         <v>3300</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>88</v>
@@ -2356,10 +2356,10 @@
         <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>106.9</v>
@@ -2437,25 +2437,25 @@
         <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-450</v>
+        <v>-550</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>72.3</v>
+        <v>64.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-430</v>
+        <v>-550</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>75</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2800</v>
+        <v>2550</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>624</v>
+        <v>566</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>116.7</v>
+        <v>106.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2280</v>
+        <v>2300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>61.6</v>
+        <v>62.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1420</v>
+        <v>-1400</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>112.2</v>
+        <v>109.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -2773,7 +2773,7 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>65</v>
@@ -2782,16 +2782,16 @@
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-49</v>
+        <v>-47</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>145.9</v>
+        <v>147.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>167</v>
+        <v>170.1</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>930</v>
+        <v>900</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-55</v>
+        <v>-85</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
@@ -2986,10 +2986,10 @@
         <v>800</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>133.3</v>
@@ -3067,25 +3067,25 @@
         <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>70.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3112,10 +3112,10 @@
         <v>1000</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>105.3</v>
@@ -3235,25 +3235,25 @@
         <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
@@ -3322,10 +3322,10 @@
         <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>80</v>
@@ -3361,25 +3361,25 @@
         <v>179</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>111.4</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>29.7</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -3403,19 +3403,19 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>2.6</v>
@@ -3445,25 +3445,25 @@
         <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>291</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>96.2</v>
+        <v>93.8</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>127.5</v>
+        <v>120.6</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>41.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1670</v>
+        <v>1700</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>66.8</v>
+        <v>68</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-830</v>
+        <v>-800</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1860</v>
+        <v>1800</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -3700,10 +3700,10 @@
         <v>700</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>77.8</v>
@@ -3739,25 +3739,25 @@
         <v>274</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>109.7</v>
+        <v>106.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -3826,10 +3826,10 @@
         <v>400</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>61.5</v>
@@ -3865,25 +3865,25 @@
         <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>95.8</v>
+        <v>84.5</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-30</v>
+        <v>-110</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>260</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>215</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>624</v>
+        <v>538</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>103.6</v>
+        <v>89.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>83.3</v>
+        <v>78.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-500</v>
+        <v>-650</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-160</v>
+        <v>-100</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
@@ -4117,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>93</v>
@@ -4126,10 +4126,10 @@
         <v>150</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>146.8</v>
+        <v>147.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>4.7</v>
@@ -4159,25 +4159,25 @@
         <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>123.8</v>
+        <v>119.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -4204,10 +4204,10 @@
         <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>78.7</v>
@@ -4243,25 +4243,25 @@
         <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1600</v>
+        <v>1560</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>164.9</v>
+        <v>160.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>195.8</v>
+        <v>188.7</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.15.pdf</t>
+          <t>Revenue Meeting_2026.09.22.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16T08:50:02.774805Z</t>
+          <t>2026-09-28T08:35:03.553301Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.15</t>
+          <t>2026.09.22</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,22 +550,22 @@
         <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13923</v>
+        <v>14745</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2346</v>
+        <v>2504</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>79.3</v>
+        <v>91.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2425.3</v>
+        <v>2595.2</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2730</v>
+        <v>2855</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>625</v>
+        <v>663</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>79.8</v>
+        <v>83.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>18.7</v>
+        <v>20.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>643.7</v>
+        <v>683.1</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1774</v>
+        <v>1916</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>80.3</v>
+        <v>86.7</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>614.3</v>
+        <v>664.3</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>85.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1182.5</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2286</v>
+        <v>2271</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>783.2</v>
+        <v>776.6</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>376.3</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17719</v>
+        <v>18075</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>225</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3993</v>
+        <v>4067</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>105.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4098.5</v>
+        <v>4172.5</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8065</v>
+        <v>8401</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1564</v>
+        <v>1625</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>75.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>25.5</v>
+        <v>28.2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1589.5</v>
+        <v>1653.2</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14363</v>
+        <v>14909</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3024</v>
+        <v>3127</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>80.3</v>
+        <v>83.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>51.9</v>
+        <v>56.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3075.9</v>
+        <v>3183.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10790</v>
+        <v>10670</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1803</v>
+        <v>1794</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1883.4</v>
+        <v>1874.3</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10965</v>
+        <v>10960</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2572</v>
+        <v>2564</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>119.2</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2619.5</v>
+        <v>2610.8</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>657</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4575</v>
+        <v>4510</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>107.6</v>
+        <v>106.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>785.2</v>
+        <v>776.4</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7431</v>
+        <v>7506</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>172</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1281</v>
+        <v>1295</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>95.3</v>
+        <v>96.2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1376.7</v>
+        <v>1388.5</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7570</v>
+        <v>7646</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>172</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1303</v>
+        <v>1314</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>97.3</v>
+        <v>97.8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1400.3</v>
+        <v>1411.8</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4071</v>
+        <v>4207</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>266</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1083</v>
+        <v>1117</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>83.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>50.9</v>
+        <v>54</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1133.9</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="18">
@@ -1066,16 +1066,16 @@
         <v>234</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>73.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>92.2</v>
+        <v>95.7</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1563.2</v>
+        <v>1570.7</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8100</v>
+        <v>8170</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1719</v>
+        <v>1726</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>73.8</v>
+        <v>74.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1746.8</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8150</v>
+        <v>8325</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>168</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1366</v>
+        <v>1402</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>89</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1376.1</v>
+        <v>1412.3</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5725</v>
+        <v>5870</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1046</v>
+        <v>1090</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>82.7</v>
+        <v>84.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1065.1</v>
+        <v>1110.6</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13210</v>
+        <v>13870</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2042</v>
+        <v>2195</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>105.4</v>
+        <v>115.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2147.4</v>
+        <v>2310.2</v>
       </c>
     </row>
     <row r="23">
@@ -1230,7 +1230,7 @@
         <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5538</v>
+        <v>5537</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94</v>
@@ -1242,10 +1242,10 @@
         <v>94.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>29</v>
+        <v>27.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>548</v>
+        <v>546.2</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7980</v>
+        <v>8046</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2554</v>
+        <v>2570</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2562.5</v>
+        <v>2578.7</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2100</v>
+        <v>2153</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>97.7</v>
+        <v>100.1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>520.6</v>
+        <v>535.3</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>34505</v>
+        <v>35295</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1012.9</v>
+        <v>1049.7</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>35517.9</v>
+        <v>36344.7</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>27263</v>
+        <v>28334</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5894</v>
+        <v>6137</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>81.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>60468</v>
+        <v>61714</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>201</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12170</v>
+        <v>12428</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>84.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>27085</v>
+        <v>28065</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4454</v>
+        <v>4687</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>86.2</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>55090</v>
+        <v>55367</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>218</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>11988</v>
+        <v>12043</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>86.40000000000001</v>
+        <v>86.8</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>494</v>
+        <v>609</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>55.2</v>
+        <v>69</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1950</v>
+        <v>-1350</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>204</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>86.7</v>
+        <v>106.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>104</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>427.5</v>
+        <v>424</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>810</v>
+        <v>880</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>88</v>
+        <v>95.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-110</v>
+        <v>-40</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>298</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>40.8</v>
+        <v>46.5</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-420</v>
+        <v>-380</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>358</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>61.5</v>
+        <v>66.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-250</v>
+        <v>-220</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-270</v>
+        <v>-200</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>80</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-140</v>
+        <v>-50</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-140</v>
+        <v>-120</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>354</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>73.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-110</v>
+        <v>-95</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2185,25 +2185,25 @@
         <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>72</v>
+        <v>66.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-126</v>
+        <v>-150</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -2230,10 +2230,10 @@
         <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>110</v>
@@ -2269,25 +2269,25 @@
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -2314,10 +2314,10 @@
         <v>3300</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>88</v>
@@ -2356,10 +2356,10 @@
         <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>106.9</v>
@@ -2437,25 +2437,25 @@
         <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-550</v>
+        <v>-450</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>64.5</v>
+        <v>72.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-550</v>
+        <v>-430</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2550</v>
+        <v>2800</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>566</v>
+        <v>624</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>106.2</v>
+        <v>116.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2300</v>
+        <v>2280</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1400</v>
+        <v>-1420</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>109.8</v>
+        <v>112.2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="32">
@@ -2773,7 +2773,7 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>65</v>
@@ -2782,16 +2782,16 @@
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-47</v>
+        <v>-49</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2160</v>
+        <v>2130</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>147.9</v>
+        <v>145.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1650</v>
+        <v>1620</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>170.1</v>
+        <v>167</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-85</v>
+        <v>-55</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2986,10 +2986,10 @@
         <v>800</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>133.3</v>
@@ -3067,25 +3067,25 @@
         <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="40">
@@ -3112,10 +3112,10 @@
         <v>1000</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>105.3</v>
@@ -3235,25 +3235,25 @@
         <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44">
@@ -3322,10 +3322,10 @@
         <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>80</v>
@@ -3361,25 +3361,25 @@
         <v>179</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>100</v>
+        <v>111.4</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>26.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="47">
@@ -3403,19 +3403,19 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-124</v>
+        <v>-123</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>2.6</v>
@@ -3445,25 +3445,25 @@
         <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>291</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>93.8</v>
+        <v>96.2</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H49" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="J49" s="3" t="n">
         <v>280</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>210</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>39.2</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1700</v>
+        <v>1670</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>68</v>
+        <v>66.8</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-800</v>
+        <v>-830</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1800</v>
+        <v>1860</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="53">
@@ -3700,10 +3700,10 @@
         <v>700</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>77.8</v>
@@ -3739,25 +3739,25 @@
         <v>274</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>106.5</v>
+        <v>109.7</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3826,10 +3826,10 @@
         <v>400</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>61.5</v>
@@ -3865,25 +3865,25 @@
         <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>84.5</v>
+        <v>95.8</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-110</v>
+        <v>-30</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>260</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>13.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>215</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>538</v>
+        <v>624</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>89.3</v>
+        <v>103.6</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-650</v>
+        <v>-500</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>86.2</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>85.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-100</v>
+        <v>-160</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="64">
@@ -4117,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>93</v>
@@ -4126,10 +4126,10 @@
         <v>150</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>147.3</v>
+        <v>146.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>4.7</v>
@@ -4159,25 +4159,25 @@
         <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>956</v>
+        <v>990</v>
       </c>
       <c r="G65" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H65" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="H65" s="3" t="n">
-        <v>72</v>
-      </c>
       <c r="I65" s="4" t="n">
-        <v>119.5</v>
+        <v>123.8</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4204,10 +4204,10 @@
         <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="I66" s="4" t="n">
         <v>78.7</v>
@@ -4243,25 +4243,25 @@
         <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1560</v>
+        <v>1600</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>160.8</v>
+        <v>164.9</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>188.7</v>
+        <v>195.8</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.15.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28T08:35:03.553301Z</t>
+          <t>2026-09-16T08:50:02.774805Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.15</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.29.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28T08:35:03.553301Z</t>
+          <t>2026-09-30T08:13:33.879264Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.29</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.29.pdf</t>
+          <t>Revenue Meeting_2026.09.22.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30T08:13:33.879264Z</t>
+          <t>2026-09-28T08:35:03.553301Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.29</t>
+          <t>2026.09.22</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.29.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28T08:35:03.553301Z</t>
+          <t>2026-09-30T08:13:33.879264Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.29</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-09</t>
+          <t>RM FCST - 2026-10</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>17100</v>
+        <v>19900</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2410</v>
+        <v>3635</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13923</v>
+        <v>12672</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2346</v>
+        <v>2433</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>79.3</v>
+        <v>48.8</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2425.3</v>
+        <v>2481.8</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3420</v>
+        <v>4000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>833</v>
+        <v>1150</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2730</v>
+        <v>2175</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>625</v>
+        <v>535</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>79.8</v>
+        <v>54.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>643.7</v>
+        <v>543.7</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2210</v>
+        <v>2708</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>752</v>
+        <v>903</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1774</v>
+        <v>2008</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>604</v>
+        <v>708</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>80.3</v>
+        <v>74.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>614.3</v>
+        <v>715.5</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4500</v>
+        <v>6350</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1188</v>
+        <v>1958</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3847</v>
+        <v>4655</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1168</v>
+        <v>1496</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85.5</v>
+        <v>73.3</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1182.5</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2732</v>
+        <v>3002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>841</v>
+        <v>982</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2286</v>
+        <v>2803</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>776</v>
+        <v>969</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>83.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>783.2</v>
+        <v>977.8</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3355</v>
+        <v>3905</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2703</v>
+        <v>3710</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>374</v>
+        <v>511</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>376.3</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20345</v>
+        <v>26940</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4445</v>
+        <v>5594</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17719</v>
+        <v>25018</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3993</v>
+        <v>5411</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>105.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4098.5</v>
+        <v>5504.4</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10645</v>
+        <v>11650</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1924</v>
+        <v>2299</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8065</v>
+        <v>9367</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1564</v>
+        <v>1830</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>75.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>25.5</v>
+        <v>21.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1589.5</v>
+        <v>1851.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>17890</v>
+        <v>19150</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3730</v>
+        <v>3905</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14363</v>
+        <v>14982</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3024</v>
+        <v>3189</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>80.3</v>
+        <v>78.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>51.9</v>
+        <v>36.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3075.9</v>
+        <v>3225.5</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12830</v>
+        <v>19950</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2051</v>
+        <v>3240</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10790</v>
+        <v>14235</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1803</v>
+        <v>2488</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1883.4</v>
+        <v>2526.3</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9195</v>
+        <v>9170</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>229</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2109</v>
+        <v>2097</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10965</v>
+        <v>11425</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2572</v>
+        <v>2677</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>119.2</v>
+        <v>124.6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47.5</v>
+        <v>35.7</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2619.5</v>
+        <v>2712.7</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4250</v>
+        <v>7400</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>657</v>
+        <v>1256</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4575</v>
+        <v>7185</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>767</v>
+        <v>1271</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>107.6</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18.2</v>
+        <v>32.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>785.2</v>
+        <v>1303.9</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7800</v>
+        <v>10210</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1280</v>
+        <v>1713</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7431</v>
+        <v>9418</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1281</v>
+        <v>1713</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>95.3</v>
+        <v>92.2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>95.7</v>
+        <v>76.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1376.7</v>
+        <v>1789.7</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9000</v>
+        <v>10690</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1444</v>
+        <v>1725</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7570</v>
+        <v>9106</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1303</v>
+        <v>1577</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>97.3</v>
+        <v>90.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1400.3</v>
+        <v>1667.2</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4860</v>
+        <v>7255</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1204</v>
+        <v>1905</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4071</v>
+        <v>5774</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1083</v>
+        <v>1494</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>83.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>50.9</v>
+        <v>35.4</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1133.9</v>
+        <v>1529.4</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>8570</v>
+        <v>10910</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1769</v>
+        <v>2385</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6291</v>
+        <v>7894</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1471</v>
+        <v>1806</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>92.2</v>
+        <v>47.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1563.2</v>
+        <v>1853.5</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10970</v>
+        <v>14420</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2176</v>
+        <v>3040</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8100</v>
+        <v>9270</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1719</v>
+        <v>2046</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>73.8</v>
+        <v>64.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27.8</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1746.8</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9160</v>
+        <v>10440</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1515</v>
+        <v>1769</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8150</v>
+        <v>10007</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1366</v>
+        <v>1753</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>89</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1376.1</v>
+        <v>1762.9</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6920</v>
+        <v>8430</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1404</v>
+        <v>1690</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5725</v>
+        <v>8181</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1046</v>
+        <v>1556</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>82.7</v>
+        <v>97</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19.1</v>
+        <v>24.9</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1065.1</v>
+        <v>1580.9</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>15350</v>
+        <v>16480</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2094</v>
+        <v>2158</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13210</v>
+        <v>16970</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2042</v>
+        <v>2653</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>103</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>105.4</v>
+        <v>147.8</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2147.4</v>
+        <v>2800.8</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5845</v>
+        <v>6370</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5538</v>
+        <v>6451</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>519</v>
+        <v>705</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>94.7</v>
+        <v>101.3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>29</v>
+        <v>11.4</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>548</v>
+        <v>716.4</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11080</v>
+        <v>11550</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3451</v>
+        <v>3653</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>7980</v>
+        <v>8703</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2554</v>
+        <v>2824</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>72</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2562.5</v>
+        <v>2830.6</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2150</v>
+        <v>2170</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2100</v>
+        <v>2160</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>97.7</v>
+        <v>99.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>520.6</v>
+        <v>557.5</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>34505</v>
+        <v>42188</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1012.9</v>
+        <v>840.3</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>35517.9</v>
+        <v>43028.3</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>33317</v>
+        <v>39865</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6453</v>
+        <v>9119</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>27263</v>
+        <v>28023</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5894</v>
+        <v>6652</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>81.8</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>71660</v>
+        <v>90070</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>13972</v>
+        <v>17293</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>60468</v>
+        <v>75180</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12170</v>
+        <v>15174</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>84.40000000000001</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>31430</v>
+        <v>35350</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5013</v>
+        <v>5618</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>27085</v>
+        <v>35158</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4454</v>
+        <v>5962</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>86.2</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>63770</v>
+        <v>77765</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>13382</v>
+        <v>16680</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>55090</v>
+        <v>65808</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>11988</v>
+        <v>14399</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>86.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-09</t>
+          <t>RM FCST 세그먼트별 - 2026-10</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4350</v>
+        <v>4200</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>692</v>
+        <v>903</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>494</v>
+        <v>621</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>55.2</v>
+        <v>64.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1950</v>
+        <v>-1500</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>37.5</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>86.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-200</v>
+        <v>-350</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5">
@@ -1633,31 +1633,31 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>855</v>
+        <v>232</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>427.5</v>
+        <v>116</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>655</v>
+        <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>29.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>920</v>
+        <v>1090</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>251</v>
+        <v>336</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>231</v>
+        <v>367</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>810</v>
+        <v>550</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>88</v>
+        <v>50.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-110</v>
+        <v>-540</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>710</v>
+        <v>640</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>298</v>
-      </c>
       <c r="H7" s="3" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>40.8</v>
+        <v>54.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-420</v>
+        <v>-290</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-250</v>
+        <v>-350</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>110</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>950</v>
+        <v>1300</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>280</v>
+        <v>367</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>266</v>
+        <v>477</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>680</v>
+        <v>900</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>248</v>
+        <v>342</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-270</v>
+        <v>-400</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>284</v>
+        <v>361</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>560</v>
+        <v>850</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>186</v>
+        <v>319</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>80</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-140</v>
+        <v>-50</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
@@ -2017,25 +2017,25 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2053,31 +2053,31 @@
         <v>600</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-140</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>73.8</v>
+        <v>112.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-110</v>
+        <v>50</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-126</v>
+        <v>-240</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -2218,34 +2218,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>110</v>
+        <v>112.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -2260,34 +2260,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>30.9</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>54</v>
+        <v>-38</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3750</v>
+        <v>5140</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1009</v>
+        <v>1299</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>282</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>931</v>
+        <v>1015</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-450</v>
+        <v>-1540</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>25.2</v>
+        <v>21</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>83</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2900</v>
+        <v>2580</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>652</v>
+        <v>600</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>704</v>
+        <v>784</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>106.9</v>
+        <v>124</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>200</v>
+        <v>620</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>21.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="23">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>95</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" s="4" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-27</v>
+        <v>-146</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>39</v>
+        <v>43.3</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>320</v>
+        <v>411</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>1100</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>66.7</v>
+        <v>62.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-550</v>
+        <v>-650</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1550</v>
+        <v>1050</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>194</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>64.5</v>
+        <v>85.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-550</v>
+        <v>-150</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="26">
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1100</v>
+        <v>-1150</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>516</v>
+        <v>331</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2550</v>
+        <v>1900</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>566</v>
+        <v>412</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>106.2</v>
+        <v>118.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>55.9</v>
+        <v>27.3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3700</v>
+        <v>5050</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>652</v>
+        <v>873</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2300</v>
+        <v>2830</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>454</v>
+        <v>608</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>62.2</v>
+        <v>56</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1400</v>
+        <v>-2220</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>22.6</v>
+        <v>10.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>51.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2050</v>
+        <v>2200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2250</v>
+        <v>2280</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>109.8</v>
+        <v>103.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>22</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>76.5</v>
+        <v>57.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-47</v>
+        <v>-206</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>42.5</v>
+        <v>3.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1460</v>
+        <v>1450</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2160</v>
+        <v>1550</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>594</v>
+        <v>440</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>147.9</v>
+        <v>106.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>970</v>
+        <v>940</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>170.1</v>
+        <v>159.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>680</v>
+        <v>560</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>985</v>
+        <v>1320</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>900</v>
+        <v>1310</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-85</v>
+        <v>-10</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>133.3</v>
+        <v>138.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>11.4</v>
+        <v>17</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9</v>
+        <v>-15</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1650</v>
+        <v>2250</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>309</v>
+        <v>404</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>105.3</v>
+        <v>68.2</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>50</v>
+        <v>-350</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>23.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="41">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
@@ -3187,31 +3187,31 @@
         <v>1500</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1150</v>
+        <v>1270</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>76.7</v>
+        <v>84.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-350</v>
+        <v>-230</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>50.1</v>
+        <v>47.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>57.6</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>100</v>
+        <v>105.3</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="44">
@@ -3268,34 +3268,34 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1440</v>
+        <v>186.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>23</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="45">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>80</v>
+        <v>53.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-100</v>
+        <v>-370</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>60.3</v>
+        <v>35.5</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>24.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="46">
@@ -3352,22 +3352,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>100</v>
@@ -3376,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>38</v>
+        <v>15.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>26.6</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>34.7</v>
+        <v>142</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-124</v>
+        <v>63</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2.6</v>
+        <v>28.7</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="48">
@@ -3439,31 +3439,31 @@
         <v>1300</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>43.2</v>
+        <v>26.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>52.6</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1020</v>
+        <v>1330</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1230</v>
+        <v>1100</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>120.6</v>
+        <v>82.7</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>210</v>
+        <v>-230</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>31.9</v>
+        <v>11.5</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>39.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="50">
@@ -3529,25 +3529,25 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>27.3</v>
+        <v>14.1</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51">
@@ -3565,31 +3565,31 @@
         <v>2500</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>13.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3607,31 +3607,31 @@
         <v>1500</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1800</v>
+        <v>1760</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>120</v>
+        <v>117.3</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>37.8</v>
+        <v>124.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
@@ -3691,31 +3691,31 @@
         <v>900</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1650</v>
+        <v>1400</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>106.5</v>
+        <v>93.3</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3781,25 +3781,25 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>73</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-46</v>
+        <v>-24</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="57">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>650</v>
+        <v>760</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>61.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-250</v>
+        <v>-210</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>19.2</v>
+        <v>25.8</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>7.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>710</v>
+        <v>870</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>84.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>-110</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>226</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>57.1</v>
+        <v>65.5</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>17.3</v>
+        <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>13.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>515</v>
+        <v>438</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>538</v>
+        <v>629</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>89.3</v>
+        <v>103.8</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2350</v>
+        <v>3500</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-650</v>
+        <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>36.7</v>
+        <v>37.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>86.2</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>700</v>
+        <v>810</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>85.7</v>
+        <v>80.2</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-100</v>
+        <v>-160</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>30.8</v>
+        <v>5.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1620</v>
+        <v>1700</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>147.3</v>
+        <v>170</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="65">
@@ -4153,31 +4153,31 @@
         <v>800</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>956</v>
+        <v>1423</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>119.5</v>
+        <v>177.9</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>156</v>
+        <v>623</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1780</v>
+        <v>1790</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-380</v>
+        <v>-390</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1560</v>
+        <v>1350</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>160.8</v>
+        <v>150</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>590</v>
+        <v>450</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="68">
@@ -4285,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="69">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>240</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>130</v>
+        <v>112.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>670</v>
+        <v>550</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>134</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>188.7</v>
+        <v>150.7</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-10</t>
+          <t>RM FCST - 2026-09</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19900</v>
+        <v>17100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3635</v>
+        <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12672</v>
+        <v>13923</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2433</v>
+        <v>2346</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>63.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>48.8</v>
+        <v>79.3</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2481.8</v>
+        <v>2425.3</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4000</v>
+        <v>3420</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1150</v>
+        <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2175</v>
+        <v>2730</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>535</v>
+        <v>625</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>54.4</v>
+        <v>79.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>543.7</v>
+        <v>643.7</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2708</v>
+        <v>2210</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>903</v>
+        <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2008</v>
+        <v>1774</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>708</v>
+        <v>604</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>74.2</v>
+        <v>80.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>715.5</v>
+        <v>614.3</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6350</v>
+        <v>4500</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1958</v>
+        <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4655</v>
+        <v>3847</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1496</v>
+        <v>1168</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>73.3</v>
+        <v>85.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1512.1</v>
+        <v>1182.5</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3002</v>
+        <v>2732</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>982</v>
+        <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2803</v>
+        <v>2286</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>969</v>
+        <v>776</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>977.8</v>
+        <v>783.2</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3905</v>
+        <v>3355</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>492</v>
+        <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3710</v>
+        <v>2703</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>511</v>
+        <v>374</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>512</v>
+        <v>376.3</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>26940</v>
+        <v>20345</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5594</v>
+        <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>25018</v>
+        <v>17719</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5411</v>
+        <v>3993</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5504.4</v>
+        <v>4098.5</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11650</v>
+        <v>10645</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2299</v>
+        <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9367</v>
+        <v>8065</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1830</v>
+        <v>1564</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21.7</v>
+        <v>25.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1851.7</v>
+        <v>1589.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19150</v>
+        <v>17890</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3905</v>
+        <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14982</v>
+        <v>14363</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3189</v>
+        <v>3024</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>78.2</v>
+        <v>80.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>36.5</v>
+        <v>51.9</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3225.5</v>
+        <v>3075.9</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19950</v>
+        <v>12830</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3240</v>
+        <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>14235</v>
+        <v>10790</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2488</v>
+        <v>1803</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>38.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2526.3</v>
+        <v>1883.4</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9170</v>
+        <v>9195</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>229</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2097</v>
+        <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11425</v>
+        <v>10965</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2677</v>
+        <v>2572</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>124.6</v>
+        <v>119.2</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>35.7</v>
+        <v>47.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2712.7</v>
+        <v>2619.5</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7400</v>
+        <v>4250</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1256</v>
+        <v>657</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7185</v>
+        <v>4575</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1271</v>
+        <v>767</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>107.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>32.9</v>
+        <v>18.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1303.9</v>
+        <v>785.2</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10210</v>
+        <v>7800</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1713</v>
+        <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9418</v>
+        <v>7431</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1713</v>
+        <v>1281</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>92.2</v>
+        <v>95.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>76.7</v>
+        <v>95.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1789.7</v>
+        <v>1376.7</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10690</v>
+        <v>9000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1725</v>
+        <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9106</v>
+        <v>7570</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1577</v>
+        <v>1303</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>85.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>90.2</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1667.2</v>
+        <v>1400.3</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7255</v>
+        <v>4860</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1905</v>
+        <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5774</v>
+        <v>4071</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1494</v>
+        <v>1083</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>35.4</v>
+        <v>50.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1529.4</v>
+        <v>1133.9</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10910</v>
+        <v>8570</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2385</v>
+        <v>1769</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7894</v>
+        <v>6291</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1806</v>
+        <v>1471</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>47.5</v>
+        <v>92.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1853.5</v>
+        <v>1563.2</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>14420</v>
+        <v>10970</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3040</v>
+        <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9270</v>
+        <v>8100</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2046</v>
+        <v>1719</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>64.3</v>
+        <v>73.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26</v>
+        <v>27.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2072</v>
+        <v>1746.8</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10440</v>
+        <v>9160</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1769</v>
+        <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10007</v>
+        <v>8150</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1753</v>
+        <v>1366</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1762.9</v>
+        <v>1376.1</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8430</v>
+        <v>6920</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1690</v>
+        <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8181</v>
+        <v>5725</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1556</v>
+        <v>1046</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>97</v>
+        <v>82.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.9</v>
+        <v>19.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1580.9</v>
+        <v>1065.1</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16480</v>
+        <v>15350</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2158</v>
+        <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16970</v>
+        <v>13210</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2653</v>
+        <v>2042</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>103</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>147.8</v>
+        <v>105.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2800.8</v>
+        <v>2147.4</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6370</v>
+        <v>5845</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6451</v>
+        <v>5538</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>705</v>
+        <v>519</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>101.3</v>
+        <v>94.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>11.4</v>
+        <v>29</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>716.4</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11550</v>
+        <v>11080</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3653</v>
+        <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8703</v>
+        <v>7980</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2824</v>
+        <v>2554</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2830.6</v>
+        <v>2562.5</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2170</v>
+        <v>2150</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2160</v>
+        <v>2100</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>99.5</v>
+        <v>97.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>557.5</v>
+        <v>520.6</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>42188</v>
+        <v>34505</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>840.3</v>
+        <v>1012.9</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>43028.3</v>
+        <v>35517.9</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>39865</v>
+        <v>33317</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9119</v>
+        <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>28023</v>
+        <v>27263</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6652</v>
+        <v>5894</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>70.3</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>90070</v>
+        <v>71660</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>17293</v>
+        <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>75180</v>
+        <v>60468</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>15174</v>
+        <v>12170</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>83.5</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>35350</v>
+        <v>31430</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5618</v>
+        <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>35158</v>
+        <v>27085</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5962</v>
+        <v>4454</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>99.5</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>77765</v>
+        <v>63770</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>16680</v>
+        <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>65808</v>
+        <v>55090</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>14399</v>
+        <v>11988</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>84.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-10</t>
+          <t>RM FCST 세그먼트별 - 2026-09</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4200</v>
+        <v>4350</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>903</v>
+        <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>621</v>
+        <v>494</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>64.3</v>
+        <v>55.2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1500</v>
+        <v>-1950</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>30.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-350</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1633,31 +1633,31 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>232</v>
+        <v>855</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>116</v>
+        <v>427.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>32</v>
+        <v>655</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>8.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1090</v>
+        <v>920</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>367</v>
+        <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>550</v>
+        <v>810</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>50.5</v>
+        <v>88</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-540</v>
+        <v>-110</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>640</v>
+        <v>710</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>338</v>
+        <v>263</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>54.7</v>
+        <v>40.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-290</v>
+        <v>-420</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-350</v>
+        <v>-250</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>110</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>367</v>
+        <v>280</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>477</v>
+        <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>900</v>
+        <v>680</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>342</v>
+        <v>248</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>69.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-400</v>
+        <v>-270</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>361</v>
+        <v>284</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>325</v>
+        <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>850</v>
+        <v>560</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>375</v>
+        <v>332</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>319</v>
+        <v>186</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-50</v>
+        <v>-140</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -2017,25 +2017,25 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -2053,31 +2053,31 @@
         <v>600</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>83.3</v>
+        <v>76.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-100</v>
+        <v>-140</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>112.5</v>
+        <v>73.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>50</v>
+        <v>-110</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-240</v>
+        <v>-126</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2218,34 +2218,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>112.7</v>
+        <v>110</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2260,34 +2260,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-38</v>
+        <v>54</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5140</v>
+        <v>3750</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1299</v>
+        <v>1009</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>282</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1015</v>
+        <v>931</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1540</v>
+        <v>-450</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>21</v>
+        <v>25.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2580</v>
+        <v>2900</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>600</v>
+        <v>652</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>784</v>
+        <v>704</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>124</v>
+        <v>106.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>620</v>
+        <v>200</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>15.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>95</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-146</v>
+        <v>-27</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>43.3</v>
+        <v>39</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>1100</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>62.9</v>
+        <v>66.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-650</v>
+        <v>-550</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>15.1</v>
+        <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1050</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>194</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>85.7</v>
+        <v>64.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-150</v>
+        <v>-550</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1150</v>
+        <v>-1100</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>11.8</v>
+        <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>331</v>
+        <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1900</v>
+        <v>2550</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>412</v>
+        <v>566</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>118.8</v>
+        <v>106.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>27.3</v>
+        <v>55.9</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5050</v>
+        <v>3700</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>873</v>
+        <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2830</v>
+        <v>2300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>608</v>
+        <v>454</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>56</v>
+        <v>62.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2220</v>
+        <v>-1400</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>30.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2200</v>
+        <v>2050</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2280</v>
+        <v>2250</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>103.6</v>
+        <v>109.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>274</v>
+        <v>153</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>57.1</v>
+        <v>76.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-206</v>
+        <v>-47</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.5</v>
+        <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1550</v>
+        <v>2160</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>440</v>
+        <v>594</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>106.9</v>
+        <v>147.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>29.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>940</v>
+        <v>970</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>159.6</v>
+        <v>170.1</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1320</v>
+        <v>985</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1310</v>
+        <v>900</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>278</v>
+        <v>181</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>99.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-10</v>
+        <v>-85</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1250</v>
+        <v>800</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>138.9</v>
+        <v>133.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>17</v>
+        <v>11.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>21.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-15</v>
+        <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2250</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>404</v>
+        <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>59.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1100</v>
+        <v>950</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>68.2</v>
+        <v>105.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-350</v>
+        <v>50</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>17.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="41">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
@@ -3187,31 +3187,31 @@
         <v>1500</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1270</v>
+        <v>1150</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>84.7</v>
+        <v>76.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-230</v>
+        <v>-350</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>60.3</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>1000</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>105.3</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
@@ -3268,34 +3268,34 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>186.1</v>
+        <v>1440</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>53.8</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-370</v>
+        <v>-100</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>35.5</v>
+        <v>60.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>15.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -3352,22 +3352,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>100</v>
@@ -3376,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>15.6</v>
+        <v>38</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>14.1</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>213</v>
+        <v>66</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>142</v>
+        <v>34.7</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>63</v>
+        <v>-124</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>28.7</v>
+        <v>2.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -3439,31 +3439,31 @@
         <v>1300</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>26.5</v>
+        <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>34.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1330</v>
+        <v>1020</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1100</v>
+        <v>1230</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>82.7</v>
+        <v>120.6</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-230</v>
+        <v>210</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>11.5</v>
+        <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="50">
@@ -3529,25 +3529,25 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>14.1</v>
+        <v>27.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -3565,31 +3565,31 @@
         <v>2500</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>583</v>
+        <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -3607,31 +3607,31 @@
         <v>1500</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1760</v>
+        <v>1800</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>421</v>
+        <v>376</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>117.3</v>
+        <v>120</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>124.1</v>
+        <v>37.8</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3691,31 +3691,31 @@
         <v>900</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>93.3</v>
+        <v>106.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -3781,25 +3781,25 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>73</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-24</v>
+        <v>-46</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>760</v>
+        <v>650</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-210</v>
+        <v>-250</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>25.8</v>
+        <v>19.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>870</v>
+        <v>710</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>760</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>-110</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>226</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>65.5</v>
+        <v>57.1</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>10.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>438</v>
+        <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>629</v>
+        <v>538</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>103.8</v>
+        <v>89.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3500</v>
+        <v>2350</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>343</v>
+        <v>216</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0</v>
+        <v>-650</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>132.1</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>810</v>
+        <v>700</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>80.2</v>
+        <v>85.7</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-160</v>
+        <v>-100</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>5.8</v>
+        <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1700</v>
+        <v>1620</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>170</v>
+        <v>147.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>700</v>
+        <v>520</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="65">
@@ -4153,31 +4153,31 @@
         <v>800</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1423</v>
+        <v>956</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>177.9</v>
+        <v>119.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>623</v>
+        <v>156</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1790</v>
+        <v>1780</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-390</v>
+        <v>-380</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1350</v>
+        <v>1560</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>150</v>
+        <v>160.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>450</v>
+        <v>590</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
@@ -4285,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>240</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>112.9</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>550</v>
+        <v>670</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>134</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>150.7</v>
+        <v>188.7</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>3635</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12672</v>
+        <v>12400</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2433</v>
+        <v>2342</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>63.7</v>
+        <v>62.3</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>48.8</v>
+        <v>45.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2481.8</v>
+        <v>2387.2</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1150</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2175</v>
+        <v>1976</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>535</v>
+        <v>493</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>54.4</v>
+        <v>49.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>543.7</v>
+        <v>500.5</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>903</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>715.5</v>
+        <v>712.4</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1958</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4655</v>
+        <v>4400</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1496</v>
+        <v>1399</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>73.3</v>
+        <v>69.3</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1512.1</v>
+        <v>1413.7</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>982</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2803</v>
+        <v>2665</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>969</v>
+        <v>925</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>977.8</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>492</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3710</v>
+        <v>3902</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>512</v>
+        <v>538.9</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>5594</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>25018</v>
+        <v>26944</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5411</v>
+        <v>5793</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>105</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5504.4</v>
+        <v>5898</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>2299</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9367</v>
+        <v>9471</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1830</v>
+        <v>1859</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21.7</v>
+        <v>18.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1851.7</v>
+        <v>1877.8</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3905</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14982</v>
+        <v>14900</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>36.5</v>
+        <v>33</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3225.5</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3240</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>14235</v>
+        <v>15435</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2488</v>
+        <v>2609</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2526.3</v>
+        <v>2646.8</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2097</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11425</v>
+        <v>12300</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2677</v>
+        <v>2867</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>124.6</v>
+        <v>134.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>35.7</v>
+        <v>39.7</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2712.7</v>
+        <v>2906.7</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1256</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7185</v>
+        <v>7485</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>101.1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>32.9</v>
+        <v>36.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1303.9</v>
+        <v>1317.4</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1713</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9418</v>
+        <v>9582</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1713</v>
+        <v>1727</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>92.2</v>
+        <v>93.8</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>76.7</v>
+        <v>70.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1789.7</v>
+        <v>1797.5</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1725</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9106</v>
+        <v>9358</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1577</v>
+        <v>1625</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>85.2</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1667.2</v>
+        <v>1716.8</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1905</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5774</v>
+        <v>6000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1494</v>
+        <v>1560</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>35.4</v>
+        <v>36.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1529.4</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>2385</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7894</v>
+        <v>8041</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1806</v>
+        <v>1867</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1853.5</v>
+        <v>1912.5</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3040</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9270</v>
+        <v>9820</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>221</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2046</v>
+        <v>2169</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>64.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2072</v>
+        <v>2195.6</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1769</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10007</v>
+        <v>9914</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1753</v>
+        <v>1732</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1762.9</v>
+        <v>1741.4</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1690</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8181</v>
+        <v>8249</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1556</v>
+        <v>1540</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.9</v>
+        <v>20.4</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1580.9</v>
+        <v>1560.4</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2158</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16970</v>
+        <v>17910</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2653</v>
+        <v>2807</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>103</v>
+        <v>108.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>147.8</v>
+        <v>149.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2800.8</v>
+        <v>2956.2</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>619</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6451</v>
+        <v>6710</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>101.3</v>
+        <v>105.3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>716.4</v>
+        <v>747.8</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3653</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8703</v>
+        <v>8976</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>324</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2824</v>
+        <v>2906</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2830.6</v>
+        <v>2914.1</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>543</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2160</v>
+        <v>2083</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>99.5</v>
+        <v>96</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>14.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>557.5</v>
+        <v>541.5</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>42188</v>
+        <v>43193</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>840.3</v>
+        <v>839.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>43028.3</v>
+        <v>44032.1</v>
       </c>
     </row>
     <row r="27"/>
@@ -1555,25 +1555,25 @@
         <v>903</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>621</v>
+        <v>514</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1500</v>
+        <v>-1800</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>30.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>365</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-350</v>
+        <v>-500</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>10.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>367</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>50.5</v>
+        <v>36.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-540</v>
+        <v>-690</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>216</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>54.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-290</v>
+        <v>-220</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-350</v>
+        <v>-330</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>190</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>477</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>69.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-400</v>
+        <v>-430</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>325</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>850</v>
+        <v>710</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-50</v>
+        <v>-190</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="14">
@@ -2062,10 +2062,10 @@
         <v>500</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>83.3</v>
@@ -2101,25 +2101,25 @@
         <v>138</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>112.5</v>
+        <v>87.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -2185,19 +2185,19 @@
         <v>98</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-240</v>
+        <v>-260</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.8</v>
@@ -2227,19 +2227,19 @@
         <v>58</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>112.7</v>
+        <v>95.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>45</v>
+        <v>-15</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.5</v>
@@ -2311,25 +2311,25 @@
         <v>1299</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3600</v>
+        <v>3950</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1015</v>
+        <v>1118</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>70</v>
+        <v>76.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1540</v>
+        <v>-1190</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>600</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3200</v>
+        <v>3530</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>784</v>
+        <v>858</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>124</v>
+        <v>136.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>620</v>
+        <v>950</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>15.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>19</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>58.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-146</v>
+        <v>-83</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
@@ -2437,25 +2437,25 @@
         <v>411</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1100</v>
+        <v>930</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>62.9</v>
+        <v>53.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-650</v>
+        <v>-820</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>16.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>194</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>85.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-150</v>
+        <v>-230</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -2521,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>20.6</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -2563,25 +2563,25 @@
         <v>788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2350</v>
+        <v>2100</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1150</v>
+        <v>-1400</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>11.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>331</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>118.8</v>
+        <v>112.5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
@@ -2647,19 +2647,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>27.3</v>
@@ -2689,25 +2689,25 @@
         <v>873</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2830</v>
+        <v>2670</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>215</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>608</v>
+        <v>574</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>56</v>
+        <v>52.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2220</v>
+        <v>-2380</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>30.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>352</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2280</v>
+        <v>2650</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>433</v>
+        <v>482</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>103.6</v>
+        <v>120.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2773,19 +2773,19 @@
         <v>43</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>82</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>57.1</v>
+        <v>60.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-206</v>
+        <v>-189</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>3.5</v>
@@ -2815,25 +2815,25 @@
         <v>378</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>106.9</v>
+        <v>120.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>29.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>250</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1500</v>
+        <v>1520</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>159.6</v>
+        <v>161.7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="36">
@@ -2941,25 +2941,25 @@
         <v>257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1310</v>
+        <v>1400</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>99.2</v>
+        <v>106.1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-10</v>
+        <v>80</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>163</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1250</v>
+        <v>1420</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>138.9</v>
+        <v>157.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="38">
@@ -3025,25 +3025,25 @@
         <v>7</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>66.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>45</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>404</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>215</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>59.2</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>191</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>68.2</v>
+        <v>59.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-350</v>
+        <v>-450</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>17.5</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>7</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-100</v>
+        <v>-92</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -3193,25 +3193,25 @@
         <v>272</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1270</v>
+        <v>1150</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>84.7</v>
+        <v>76.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-230</v>
+        <v>-350</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>60.3</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="43">
@@ -3238,10 +3238,10 @@
         <v>1000</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>105.3</v>
@@ -3277,25 +3277,25 @@
         <v>4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>11.2</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="45">
@@ -3319,25 +3319,25 @@
         <v>217</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-370</v>
+        <v>-350</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>236</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>900</v>
+        <v>952</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>100</v>
+        <v>105.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="47">
@@ -3403,25 +3403,25 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>142</v>
+        <v>140.7</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>294</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>34.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>290</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>82.7</v>
+        <v>85</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-230</v>
+        <v>-200</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>11.5</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="50">
@@ -3529,25 +3529,25 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>14.1</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51">
@@ -3571,19 +3571,19 @@
         <v>583</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-900</v>
+        <v>-890</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>5.8</v>
@@ -3613,25 +3613,25 @@
         <v>323</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1760</v>
+        <v>1820</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>117.3</v>
+        <v>121.3</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>178</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>301</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>196</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-210</v>
+        <v>-330</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.8</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>214</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>760</v>
+        <v>660</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-110</v>
+        <v>-210</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3949,25 +3949,25 @@
         <v>248</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>65.5</v>
+        <v>58.6</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>438</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2700</v>
+        <v>2950</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>629</v>
+        <v>702</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>103.8</v>
+        <v>113.5</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>322</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>100</v>
+        <v>101.4</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>132.1</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>85</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>80.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-160</v>
+        <v>-60</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1700</v>
+        <v>1730</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>62</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1423</v>
+        <v>1360</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>177.9</v>
+        <v>170</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>623</v>
+        <v>560</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>647</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>367</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>78.2</v>
+        <v>83.8</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-390</v>
+        <v>-290</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>326</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>150</v>
+        <v>161.1</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -4285,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>341</v>
+        <v>251</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="69">
@@ -4327,25 +4327,25 @@
         <v>156</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>655</v>
+        <v>620</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>112.9</v>
+        <v>106.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>98</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>150.7</v>
+        <v>164.4</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.29.pdf</t>
+          <t>Revenue Meeting_2026.10.13.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30T08:13:33.879264Z</t>
+          <t>2026-10-14T10:56:18.495540Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.29</t>
+          <t>2026.10.13</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>3635</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12400</v>
+        <v>13050</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2342</v>
+        <v>2425</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>62.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>45.2</v>
+        <v>51.1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2387.2</v>
+        <v>2476.1</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1150</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1976</v>
+        <v>2147</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>49.4</v>
+        <v>53.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>500.5</v>
+        <v>531.7</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>903</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>74.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>712.4</v>
+        <v>715.6</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1958</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4400</v>
+        <v>4313</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1399</v>
+        <v>1362</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>69.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1413.7</v>
+        <v>1375.8</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>982</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2665</v>
+        <v>2587</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88.8</v>
+        <v>86.2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>933</v>
+        <v>902.4</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>492</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3902</v>
+        <v>3751</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>99.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>538.9</v>
+        <v>518.9</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>5594</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>26944</v>
+        <v>27102</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5793</v>
+        <v>5809</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100</v>
+        <v>100.6</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>105</v>
+        <v>106.9</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5898</v>
+        <v>5915.9</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>2299</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9471</v>
+        <v>9544</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>196</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>81.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1877.8</v>
+        <v>1887.4</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3905</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14900</v>
+        <v>15030</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>214</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3186</v>
+        <v>3220</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>77.8</v>
+        <v>78.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3219</v>
+        <v>3253.2</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3240</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15435</v>
+        <v>15505</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2609</v>
+        <v>2573</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2646.8</v>
+        <v>2609.7</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2097</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2867</v>
+        <v>2901</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>134.1</v>
+        <v>136.3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2906.7</v>
+        <v>2942.6</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1256</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7485</v>
+        <v>7535</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>101.1</v>
+        <v>101.8</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>36.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1317.4</v>
+        <v>1309.4</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1713</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9582</v>
+        <v>9670</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>93.8</v>
+        <v>94.7</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>70.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1797.5</v>
+        <v>1801.5</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1725</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9358</v>
+        <v>9390</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>87.5</v>
+        <v>87.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>91.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1716.8</v>
+        <v>1712.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1905</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>260</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1560</v>
+        <v>1601</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>82.7</v>
+        <v>84.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1596.9</v>
+        <v>1638.3</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>2385</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8041</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1867</v>
+        <v>1842</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>73.7</v>
+        <v>73</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>45.5</v>
+        <v>43.8</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1912.5</v>
+        <v>1885.8</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3040</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9820</v>
+        <v>9845</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2169</v>
+        <v>2160</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26.6</v>
+        <v>27.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2195.6</v>
+        <v>2187.5</v>
       </c>
     </row>
     <row r="20">
@@ -1128,13 +1128,13 @@
         <v>1769</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9914</v>
+        <v>9915</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>95</v>
@@ -1143,7 +1143,7 @@
         <v>9.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1741.4</v>
+        <v>1740.4</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1690</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8249</v>
+        <v>8182</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1540</v>
+        <v>1524</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1560.4</v>
+        <v>1544.6</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2158</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17910</v>
+        <v>18250</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2807</v>
+        <v>2893</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>108.7</v>
+        <v>110.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>149.2</v>
+        <v>147.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2956.2</v>
+        <v>3040.1</v>
       </c>
     </row>
     <row r="23">
@@ -1236,16 +1236,16 @@
         <v>110</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>105.3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>747.8</v>
+        <v>752</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3653</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8976</v>
+        <v>9260</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2906</v>
+        <v>2977</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>77.7</v>
+        <v>80.2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2914.1</v>
+        <v>2985.5</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>543</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2083</v>
+        <v>2135</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>96</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>541.5</v>
+        <v>550.8</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>43193</v>
+        <v>43436</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>839.1</v>
+        <v>842.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>44032.1</v>
+        <v>44278.1</v>
       </c>
     </row>
     <row r="27"/>
@@ -1555,25 +1555,25 @@
         <v>903</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>514</v>
+        <v>577</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1800</v>
+        <v>-1400</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>27</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -1600,10 +1600,10 @@
         <v>1300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>72.2</v>
@@ -1639,25 +1639,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>367</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>36.7</v>
+        <v>38.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-690</v>
+        <v>-670</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -1726,10 +1726,10 @@
         <v>420</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>65.59999999999999</v>
@@ -1807,25 +1807,25 @@
         <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>52.9</v>
+        <v>55</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-330</v>
+        <v>-315</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="10">
@@ -1849,19 +1849,19 @@
         <v>190</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-90</v>
+        <v>-85</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>7.1</v>
@@ -1933,25 +1933,25 @@
         <v>477</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-430</v>
+        <v>-450</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>325</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>710</v>
+        <v>630</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-190</v>
+        <v>-270</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>231</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>138</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>378</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -2227,19 +2227,19 @@
         <v>58</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>151</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>95.8</v>
+        <v>84.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-15</v>
+        <v>-55</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.5</v>
@@ -2311,25 +2311,25 @@
         <v>1299</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1118</v>
+        <v>1134</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>76.8</v>
+        <v>77.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1190</v>
+        <v>-1140</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>600</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3530</v>
+        <v>3500</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>243</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>136.8</v>
+        <v>135.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>950</v>
+        <v>920</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>19</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>82</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>58.5</v>
+        <v>70</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-83</v>
+        <v>-60</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="24">
@@ -2437,25 +2437,25 @@
         <v>411</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>53.1</v>
+        <v>52</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-820</v>
+        <v>-840</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>194</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-230</v>
+        <v>-250</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
@@ -2566,10 +2566,10 @@
         <v>2100</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>60</v>
@@ -2605,25 +2605,25 @@
         <v>331</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1800</v>
+        <v>1840</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>112.5</v>
+        <v>115</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>873</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2670</v>
+        <v>2600</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>574</v>
+        <v>551</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2380</v>
+        <v>-2450</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>352</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2650</v>
+        <v>2530</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>120.5</v>
+        <v>115</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>450</v>
+        <v>330</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>43</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>82</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-189</v>
+        <v>-160</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>378</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>120.7</v>
+        <v>127.6</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>250</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>161.7</v>
+        <v>160.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35">
@@ -2902,10 +2902,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
@@ -2941,25 +2941,25 @@
         <v>257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>106.1</v>
+        <v>102.3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>163</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>157.8</v>
+        <v>158.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="38">
@@ -3025,25 +3025,25 @@
         <v>7</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>45</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="39">
@@ -3112,10 +3112,10 @@
         <v>650</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>59.1</v>
@@ -3193,25 +3193,25 @@
         <v>272</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>76.7</v>
+        <v>73.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-350</v>
+        <v>-400</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>54.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>158</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>105.3</v>
+        <v>109.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18.8</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="44">
@@ -3277,25 +3277,25 @@
         <v>4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>18.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="45">
@@ -3319,25 +3319,25 @@
         <v>217</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>56.2</v>
+        <v>55</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-350</v>
+        <v>-360</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>236</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>105.8</v>
+        <v>107.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="47">
@@ -3403,25 +3403,25 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>140.7</v>
+        <v>152</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>294</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>290</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1130</v>
+        <v>1100</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>250</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>85</v>
+        <v>82.7</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-200</v>
+        <v>-230</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>11.5</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>583</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1610</v>
+        <v>1550</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-890</v>
+        <v>-950</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -3616,10 +3616,10 @@
         <v>1820</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>121.3</v>
@@ -3655,25 +3655,25 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="H53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>124.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54">
@@ -3697,25 +3697,25 @@
         <v>178</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>147</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>77.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-200</v>
+        <v>-215</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>301</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-150</v>
+        <v>-120</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>196</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>56.6</v>
+        <v>59.2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-330</v>
+        <v>-310</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.8</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>214</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-210</v>
+        <v>-230</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3949,25 +3949,25 @@
         <v>248</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>236</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>58.6</v>
+        <v>69</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-600</v>
+        <v>-450</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="61">
@@ -3991,19 +3991,19 @@
         <v>438</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2950</v>
+        <v>2980</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>113.5</v>
+        <v>114.6</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
@@ -4033,25 +4033,25 @@
         <v>322</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3550</v>
+        <v>3450</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>101.4</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>134</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>85</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-60</v>
+        <v>-10</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="64">
@@ -4159,25 +4159,25 @@
         <v>62</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1360</v>
+        <v>1329</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>170</v>
+        <v>166.1</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>647</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>83.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-290</v>
+        <v>-190</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>326</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>161.1</v>
+        <v>172.2</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="68">
@@ -4369,25 +4369,25 @@
         <v>98</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>164.4</v>
+        <v>171.2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.10.13.pdf</t>
+          <t>Revenue Meeting_2026.10.20.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14T10:56:18.495540Z</t>
+          <t>2026-10-21T08:17:46.300380Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,22 +550,22 @@
         <v>3635</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13050</v>
+        <v>13051</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2425</v>
+        <v>2418</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2476.1</v>
+        <v>2469.2</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1150</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2147</v>
+        <v>2173</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>531.7</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
@@ -621,19 +621,19 @@
         <v>2012</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>74.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>715.6</v>
+        <v>712.9</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1958</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4313</v>
+        <v>4242</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1362</v>
+        <v>1330</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1375.8</v>
+        <v>1342.9</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>982</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2587</v>
+        <v>2640</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>346</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>86.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>902.4</v>
+        <v>921.4</v>
       </c>
     </row>
     <row r="8">
@@ -720,7 +720,7 @@
         <v>492</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3751</v>
+        <v>3759</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>138</v>
@@ -729,7 +729,7 @@
         <v>518</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>96.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0.9</v>
@@ -754,22 +754,22 @@
         <v>5594</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>27102</v>
+        <v>27174</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>214</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5809</v>
+        <v>5817</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>106.9</v>
+        <v>106.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5915.9</v>
+        <v>5923.5</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>2299</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9544</v>
+        <v>9492</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>81.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1887.4</v>
+        <v>1885.3</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3905</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15030</v>
+        <v>15108</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3220</v>
+        <v>3241</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3253.2</v>
+        <v>3273.6</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3240</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15505</v>
+        <v>15720</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2573</v>
+        <v>2579</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>77.7</v>
+        <v>78.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2609.7</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2097</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12500</v>
+        <v>12570</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>232</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2901</v>
+        <v>2914</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>136.3</v>
+        <v>137.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2942.6</v>
+        <v>2955.8</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1256</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7535</v>
+        <v>7550</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>101.8</v>
+        <v>102</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>36.4</v>
+        <v>34.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1309.4</v>
+        <v>1303.9</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1713</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9670</v>
+        <v>9675</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>70.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1801.5</v>
+        <v>1793.4</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1725</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9390</v>
+        <v>9530</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1624</v>
+        <v>1643</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>87.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1712.9</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1905</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6150</v>
+        <v>6170</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1638.3</v>
+        <v>1643.5</v>
       </c>
     </row>
     <row r="18">
@@ -1066,16 +1066,16 @@
         <v>231</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1842</v>
+        <v>1836</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>73</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1885.8</v>
+        <v>1879.3</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3040</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9845</v>
+        <v>9975</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2160</v>
+        <v>2193</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>68.3</v>
+        <v>69.2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2187.5</v>
+        <v>2221.2</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1769</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9915</v>
+        <v>9787</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1731</v>
+        <v>1713</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>93.7</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1740.4</v>
+        <v>1722.3</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1690</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8182</v>
+        <v>8127</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>186</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1524</v>
+        <v>1513</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1544.6</v>
+        <v>1533.3</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2158</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>18250</v>
+        <v>18840</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2893</v>
+        <v>2978</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>110.7</v>
+        <v>114.3</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>147.1</v>
+        <v>145.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3040.1</v>
+        <v>3123.1</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>619</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6710</v>
+        <v>6722</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>105.3</v>
+        <v>105.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>752</v>
+        <v>756.2</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3653</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9260</v>
+        <v>9355</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2977</v>
+        <v>2999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>80.2</v>
+        <v>81</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2985.5</v>
+        <v>3007.8</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>543</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2135</v>
+        <v>2217</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>550.8</v>
+        <v>569.6</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>43436</v>
+        <v>43609</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>842.1</v>
+        <v>836.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>44278.1</v>
+        <v>44445.1</v>
       </c>
     </row>
     <row r="27"/>
@@ -1555,25 +1555,25 @@
         <v>903</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2800</v>
+        <v>2780</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1400</v>
+        <v>-1420</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>365</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>72.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-500</v>
+        <v>-550</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>367</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>38.5</v>
+        <v>39.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-670</v>
+        <v>-655</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -1723,19 +1723,19 @@
         <v>216</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>317</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-220</v>
+        <v>-215</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>7.1</v>
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>35</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1807,25 +1807,25 @@
         <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>55</v>
+        <v>57.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-315</v>
+        <v>-300</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>190</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>387</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-85</v>
+        <v>-80</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>477</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>850</v>
+        <v>765</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>379</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-450</v>
+        <v>-535</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>325</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>378</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-270</v>
+        <v>-275</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>231</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>75</v>
+        <v>71.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>138</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-60</v>
+        <v>-30</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2227,19 +2227,19 @@
         <v>58</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>151</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>84.5</v>
+        <v>81.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-55</v>
+        <v>-65</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.5</v>
@@ -2311,25 +2311,25 @@
         <v>1299</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4000</v>
+        <v>3920</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1134</v>
+        <v>1117</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>77.8</v>
+        <v>76.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1140</v>
+        <v>-1220</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>600</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3500</v>
+        <v>3530</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>243</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>135.7</v>
+        <v>136.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>19</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-60</v>
+        <v>-35</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="24">
@@ -2437,25 +2437,25 @@
         <v>411</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-840</v>
+        <v>-850</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>194</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>203</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>76.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-250</v>
+        <v>-230</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2100</v>
+        <v>2070</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>60</v>
+        <v>59.1</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1400</v>
+        <v>-1430</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>11.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>331</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>115</v>
+        <v>112.5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>873</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2600</v>
+        <v>2620</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2450</v>
+        <v>-2430</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>352</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2530</v>
+        <v>2575</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -2773,19 +2773,19 @@
         <v>43</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-160</v>
+        <v>-176</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>3.5</v>
@@ -2815,25 +2815,25 @@
         <v>378</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>127.6</v>
+        <v>128.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="34">
@@ -2857,19 +2857,19 @@
         <v>250</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>259</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>160.6</v>
+        <v>161.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
@@ -2941,25 +2941,25 @@
         <v>257</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1350</v>
+        <v>1320</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>102.3</v>
+        <v>100</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>163</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1425</v>
+        <v>1350</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>176</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>158.3</v>
+        <v>150</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>404</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1250</v>
+        <v>1175</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>215</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>55.6</v>
+        <v>52.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-1000</v>
+        <v>-1075</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>54.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>191</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>59.1</v>
+        <v>61.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-450</v>
+        <v>-420</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="41">
@@ -3151,7 +3151,7 @@
         <v>7</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>92</v>
@@ -3160,16 +3160,16 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-92</v>
+        <v>-84</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3193,25 +3193,25 @@
         <v>272</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>73.3</v>
+        <v>72</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-400</v>
+        <v>-420</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>52.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="43">
@@ -3277,25 +3277,25 @@
         <v>4</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="45">
@@ -3319,25 +3319,25 @@
         <v>217</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>55</v>
+        <v>53.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-360</v>
+        <v>-375</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>236</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>289</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>107.8</v>
+        <v>108.9</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="47">
@@ -3403,25 +3403,25 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>294</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>88.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -3490,10 +3490,10 @@
         <v>1100</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>82.7</v>
@@ -3529,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>11</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>14.1</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51">
@@ -3571,19 +3571,19 @@
         <v>583</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-950</v>
+        <v>-955</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>5.8</v>
@@ -3613,25 +3613,25 @@
         <v>323</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1820</v>
+        <v>1880</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>121.3</v>
+        <v>125.3</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>2</v>
@@ -3667,13 +3667,13 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>124.1</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="54">
@@ -3697,19 +3697,19 @@
         <v>178</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-215</v>
+        <v>-220</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>6.8</v>
@@ -3739,25 +3739,25 @@
         <v>301</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1380</v>
+        <v>1350</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>183</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-120</v>
+        <v>-150</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="56">
@@ -3826,10 +3826,10 @@
         <v>450</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>59.2</v>
@@ -3865,25 +3865,25 @@
         <v>214</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>73.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-230</v>
+        <v>-250</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>248</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>69</v>
+        <v>74.5</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-450</v>
+        <v>-370</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="61">
@@ -3994,10 +3994,10 @@
         <v>2980</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="I61" s="4" t="n">
         <v>114.6</v>
@@ -4033,25 +4033,25 @@
         <v>322</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3450</v>
+        <v>3375</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-50</v>
+        <v>-125</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>130.3</v>
+        <v>127.4</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>85</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>800</v>
+        <v>842</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>98.8</v>
+        <v>104</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-10</v>
+        <v>32</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="64">
@@ -4117,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1730</v>
+        <v>1738</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>110</v>
@@ -4126,10 +4126,10 @@
         <v>190</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>173</v>
+        <v>173.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>2</v>
@@ -4159,19 +4159,19 @@
         <v>62</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>103</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>166.1</v>
+        <v>164.1</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
@@ -4201,19 +4201,19 @@
         <v>647</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-190</v>
+        <v>-195</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.2</v>
@@ -4243,25 +4243,25 @@
         <v>326</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>172.2</v>
+        <v>173.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="68">
@@ -4285,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="69">
@@ -4327,25 +4327,25 @@
         <v>156</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>235</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>106.9</v>
+        <v>113.8</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>98</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>171.2</v>
+        <v>178.1</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.10.20.pdf</t>
+          <t>Revenue Meeting_2026.10.27.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21T08:17:46.300380Z</t>
+          <t>2026-10-28T08:51:25.826026Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.10.20</t>
+          <t>2026.10.27</t>
         </is>
       </c>
     </row>

--- a/data/RM_FCST_정리.xlsx
+++ b/data/RM_FCST_정리.xlsx
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-10</t>
+          <t>RM FCST - 2026-11</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>19900</v>
+        <v>12750</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3635</v>
+        <v>1750</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13051</v>
+        <v>10410</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2418</v>
+        <v>1566</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>51.2</v>
+        <v>81.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2469.2</v>
+        <v>1647.5</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4000</v>
+        <v>2465</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1150</v>
+        <v>503</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2173</v>
+        <v>1917</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>532</v>
+        <v>416</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>54.3</v>
+        <v>77.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8</v>
+        <v>22.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>540</v>
+        <v>438.1</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2708</v>
+        <v>1978</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>903</v>
+        <v>567</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2012</v>
+        <v>1795</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>705</v>
+        <v>553</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>74.3</v>
+        <v>90.7</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>712.9</v>
+        <v>561.5</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6350</v>
+        <v>4130</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1958</v>
+        <v>1041</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4242</v>
+        <v>2933</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1330</v>
+        <v>828</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>66.8</v>
+        <v>71</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1342.9</v>
+        <v>838.6</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3002</v>
+        <v>2257</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>982</v>
+        <v>654</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2640</v>
+        <v>1792</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>914</v>
+        <v>579</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>921.4</v>
+        <v>584.2</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3905</v>
+        <v>3495</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>492</v>
+        <v>410</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3759</v>
+        <v>3175</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>518</v>
+        <v>410</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>96.3</v>
+        <v>90.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>518.9</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>26940</v>
+        <v>21195</v>
       </c>
       <c r="C9" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>4304</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>20310</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>5594</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>27174</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>214</v>
-      </c>
       <c r="G9" s="3" t="n">
-        <v>5817</v>
+        <v>4215</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.9</v>
+        <v>95.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>106.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5923.5</v>
+        <v>4309.6</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11650</v>
+        <v>9830</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2299</v>
+        <v>1786</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9492</v>
+        <v>6976</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1867</v>
+        <v>1287</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>81.5</v>
+        <v>71</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18.3</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1885.3</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19150</v>
+        <v>16250</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3905</v>
+        <v>3193</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15108</v>
+        <v>12000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3241</v>
+        <v>2406</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>32.6</v>
+        <v>50.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3273.6</v>
+        <v>2456.4</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19950</v>
+        <v>14500</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3240</v>
+        <v>2183</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15720</v>
+        <v>12435</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2579</v>
+        <v>1960</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>78.8</v>
+        <v>85.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2616</v>
+        <v>1999.8</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9170</v>
+        <v>8490</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2097</v>
+        <v>1836</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12570</v>
+        <v>10870</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2914</v>
+        <v>2446</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>137.1</v>
+        <v>128</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>41.8</v>
+        <v>35.2</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2955.8</v>
+        <v>2481.2</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7400</v>
+        <v>6965</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1256</v>
+        <v>1104</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7550</v>
+        <v>7800</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1269</v>
+        <v>1248</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1303.9</v>
+        <v>1285.6</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10210</v>
+        <v>8070</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1713</v>
+        <v>1269</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9675</v>
+        <v>6920</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1725</v>
+        <v>1134</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>94.8</v>
+        <v>85.7</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1793.4</v>
+        <v>1201.8</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10690</v>
+        <v>9150</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1725</v>
+        <v>1330</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9530</v>
+        <v>8532</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1643</v>
+        <v>1360</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>89</v>
+        <v>61.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1732</v>
+        <v>1421.1</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7255</v>
+        <v>6340</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1905</v>
+        <v>1519</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6170</v>
+        <v>4784</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1607</v>
+        <v>1177</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>85</v>
+        <v>75.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1643.5</v>
+        <v>1211.3</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10910</v>
+        <v>8550</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2385</v>
+        <v>1737</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7964</v>
+        <v>6879</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1836</v>
+        <v>1442</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>73</v>
+        <v>80.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>43.3</v>
+        <v>61.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1879.3</v>
+        <v>1503.5</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>14420</v>
+        <v>11470</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3040</v>
+        <v>2350</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9975</v>
+        <v>6885</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2193</v>
+        <v>1404</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>69.2</v>
+        <v>60</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>28.2</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2221.2</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10440</v>
+        <v>8300</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1769</v>
+        <v>1293</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9787</v>
+        <v>8726</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1713</v>
+        <v>1423</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>93.7</v>
+        <v>105.1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1722.3</v>
+        <v>1431.9</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8430</v>
+        <v>6520</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1690</v>
+        <v>1272</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>8127</v>
+        <v>6443</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1513</v>
+        <v>1129</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20.3</v>
+        <v>30.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1533.3</v>
+        <v>1159.3</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16480</v>
+        <v>13910</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2158</v>
+        <v>1834</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>18840</v>
+        <v>17350</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2978</v>
+        <v>2450</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>114.3</v>
+        <v>124.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>145.1</v>
+        <v>244.6</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3123.1</v>
+        <v>2694.6</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6370</v>
+        <v>5985</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>619</v>
+        <v>554</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6722</v>
+        <v>5479</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>744</v>
+        <v>569</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>105.5</v>
+        <v>91.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>756.2</v>
+        <v>580.3</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11550</v>
+        <v>10040</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3653</v>
+        <v>2908</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9355</v>
+        <v>7200</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2999</v>
+        <v>2140</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>81</v>
+        <v>71.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3007.8</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2170</v>
+        <v>1880</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>543</v>
+        <v>394</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2217</v>
+        <v>1815</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>554</v>
+        <v>383</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>102.2</v>
+        <v>96.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>569.6</v>
+        <v>395.7</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>43609</v>
+        <v>32525</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>836.1</v>
+        <v>960</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>44445.1</v>
+        <v>33485</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>39865</v>
+        <v>27075</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9119</v>
+        <v>4925</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>28023</v>
+        <v>22954</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6652</v>
+        <v>4656</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>70.3</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="29">
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>90070</v>
+        <v>71725</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>17293</v>
+        <v>13130</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>75180</v>
+        <v>59893</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>15174</v>
+        <v>11309</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>83.5</v>
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>35350</v>
+        <v>28730</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5618</v>
+        <v>4399</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>35158</v>
+        <v>31614</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5962</v>
+        <v>4981</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>99.5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>77765</v>
+        <v>66990</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>16680</v>
+        <v>13339</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>65808</v>
+        <v>59238</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>14399</v>
+        <v>12047</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>84.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-10</t>
+          <t>RM FCST 세그먼트별 - 2026-11</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4200</v>
+        <v>2800</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>903</v>
+        <v>357</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2780</v>
+        <v>3650</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>66.2</v>
+        <v>130.4</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1420</v>
+        <v>850</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>31.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>365</v>
+        <v>148</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1250</v>
+        <v>900</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>300</v>
+        <v>158</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-550</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="5">
@@ -1633,31 +1633,31 @@
         <v>200</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>314</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>26</v>
-      </c>
       <c r="I5" s="4" t="n">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>11</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1090</v>
+        <v>630</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>336</v>
+        <v>212</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>367</v>
+        <v>133</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>435</v>
+        <v>850</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>39.9</v>
+        <v>134.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-655</v>
+        <v>220</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>640</v>
+        <v>310</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>338</v>
+        <v>211</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>425</v>
+        <v>220</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>317</v>
+        <v>234</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-215</v>
+        <v>-90</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>357</v>
+        <v>270</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>373</v>
+        <v>316</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>-300</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>470</v>
+        <v>400</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>387</v>
+        <v>326</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>85.5</v>
+        <v>133.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-80</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>367</v>
+        <v>265</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>477</v>
+        <v>239</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>379</v>
+        <v>296</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>290</v>
+        <v>207</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>58.8</v>
+        <v>77.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-535</v>
+        <v>-200</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>625</v>
+        <v>470</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-275</v>
+        <v>-30</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -2017,25 +2017,25 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>71.7</v>
+        <v>80</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-170</v>
+        <v>-100</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>345</v>
+        <v>285</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>92.5</v>
+        <v>83.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>56.7</v>
+        <v>80</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-260</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>0.8</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -2218,28 +2218,28 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>81.7</v>
+        <v>128.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-65</v>
+        <v>80</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.5</v>
@@ -2260,34 +2260,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5140</v>
+        <v>3300</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1299</v>
+        <v>844</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3920</v>
+        <v>3400</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1117</v>
+        <v>889</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>76.3</v>
+        <v>103</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1220</v>
+        <v>100</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>21</v>
+        <v>15.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2580</v>
+        <v>2230</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>600</v>
+        <v>531</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3530</v>
+        <v>3450</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>136.8</v>
+        <v>154.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>950</v>
+        <v>1220</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>16.9</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="23">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>82.5</v>
+        <v>110</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-35</v>
+        <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1750</v>
+        <v>1400</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>411</v>
+        <v>270</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>900</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>51.4</v>
+        <v>64.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-850</v>
+        <v>-500</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-230</v>
+        <v>-150</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -2521,25 +2521,25 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>2700</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>788</v>
+        <v>567</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2070</v>
+        <v>2100</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>525</v>
+        <v>479</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>59.1</v>
+        <v>77.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1430</v>
+        <v>-600</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>11.8</v>
+        <v>19.4</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>24.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>112.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>27.3</v>
+        <v>49.1</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5050</v>
+        <v>3550</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>873</v>
+        <v>596</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2620</v>
+        <v>2600</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>546</v>
+        <v>481</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>51.9</v>
+        <v>73.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2430</v>
+        <v>-950</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2575</v>
+        <v>2300</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>451</v>
+        <v>396</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>117</v>
+        <v>135.3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>63.3</v>
+        <v>127</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-176</v>
+        <v>54</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>1450</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1860</v>
-      </c>
       <c r="G33" s="3" t="n">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>518</v>
+        <v>386</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>128.3</v>
+        <v>104.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>410</v>
+        <v>65</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>35.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>940</v>
+        <v>880</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1515</v>
+        <v>1650</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>161.2</v>
+        <v>187.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>575</v>
+        <v>770</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1320</v>
+        <v>1645</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1320</v>
+        <v>1755</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>100</v>
+        <v>106.7</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>7.8</v>
+        <v>12.1</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10.4</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1350</v>
+        <v>1680</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>238</v>
+        <v>288</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>450</v>
+        <v>980</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>22.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-9</v>
+        <v>28</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>45</v>
+        <v>40.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2250</v>
+        <v>1400</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>404</v>
+        <v>247</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>52.2</v>
+        <v>85.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-1075</v>
+        <v>-200</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1100</v>
+        <v>750</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>61.8</v>
+        <v>86.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-420</v>
+        <v>-100</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="41">
@@ -3142,34 +3142,34 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-84</v>
+        <v>-150</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>72</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-420</v>
+        <v>-250</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>47.5</v>
+        <v>38</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>51.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="43">
@@ -3229,31 +3229,31 @@
         <v>950</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>109.5</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>19.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="44">
@@ -3268,34 +3268,34 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>80</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>48</v>
+        <v>-43</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>186.1</v>
+        <v>65.8</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>18.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="45">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>800</v>
+        <v>880</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>327</v>
+        <v>274</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>53.1</v>
+        <v>54.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-375</v>
+        <v>-400</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>35.5</v>
+        <v>44.6</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>15.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="46">
@@ -3355,31 +3355,31 @@
         <v>900</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>980</v>
+        <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>283</v>
+        <v>212</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>108.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>80</v>
+        <v>-100</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>142</v>
+        <v>128.1</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>28.7</v>
+        <v>1.5</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1130</v>
+        <v>900</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>331</v>
+        <v>221</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-170</v>
+        <v>-200</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>26.5</v>
+        <v>48.6</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>30</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1330</v>
+        <v>900</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>82.7</v>
+        <v>111.1</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-230</v>
+        <v>100</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>11.5</v>
+        <v>17.7</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="50">
@@ -3529,25 +3529,25 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>14.1</v>
+        <v>64.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>583</v>
+        <v>542</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1545</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>381</v>
+        <v>290</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>61.8</v>
+        <v>52.1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-955</v>
+        <v>-1150</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="52">
@@ -3607,31 +3607,31 @@
         <v>1500</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1880</v>
+        <v>1150</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>445</v>
+        <v>250</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>125.3</v>
+        <v>76.7</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>380</v>
+        <v>-350</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>17.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="53">
@@ -3655,25 +3655,25 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>124.1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>900</v>
+        <v>550</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>109.1</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-220</v>
+        <v>50</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1500</v>
+        <v>730</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>301</v>
+        <v>124</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>90</v>
+        <v>130.1</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-150</v>
+        <v>220</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="56">
@@ -3781,25 +3781,25 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>73</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-24</v>
+        <v>-64</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="57">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>760</v>
+        <v>520</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>59.2</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-310</v>
+        <v>0</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>25.8</v>
+        <v>34.4</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>11.6</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>870</v>
+        <v>680</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>71.3</v>
+        <v>102.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-250</v>
+        <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>14</v>
+        <v>17.7</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>74.5</v>
+        <v>92.3</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-370</v>
+        <v>-100</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2980</v>
+        <v>2550</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>716</v>
+        <v>536</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>114.6</v>
+        <v>115.9</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3375</v>
+        <v>6000</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>328</v>
+        <v>606</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>200</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-125</v>
+        <v>3000</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>127.4</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>810</v>
+        <v>740</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>842</v>
+        <v>560</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>104</v>
+        <v>75.7</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>32</v>
+        <v>-180</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>5.8</v>
+        <v>11.4</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1738</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>173.8</v>
+        <v>104.2</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>738</v>
+        <v>50</v>
       </c>
       <c r="K64" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L64" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="65">
@@ -4153,31 +4153,31 @@
         <v>800</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1313</v>
+        <v>1188</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>164.1</v>
+        <v>148.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>513</v>
+        <v>388</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1790</v>
+        <v>1740</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1595</v>
+        <v>1100</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>579</v>
+        <v>398</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-195</v>
+        <v>-640</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="67">
@@ -4237,31 +4237,31 @@
         <v>900</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1560</v>
+        <v>1250</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>569</v>
+        <v>433</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>173.3</v>
+        <v>138.9</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>660</v>
+        <v>350</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="68">
@@ -4285,25 +4285,25 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>58.6</v>
+        <v>6187</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4318,25 +4318,25 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>113.8</v>
+        <v>115.4</v>
       </c>
       <c r="J69" s="3" t="n">
         <v>80</v>
@@ -4345,7 +4345,7 @@
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>178.1</v>
+        <v>140.6</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-11 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>
